--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/192.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/192.xlsx
@@ -426,13 +426,13 @@
         <v>3.343497364542479</v>
       </c>
       <c r="E2">
-        <v>-16.59604871797209</v>
+        <v>-16.96578503527635</v>
       </c>
       <c r="F2">
-        <v>-0.9023780356501352</v>
+        <v>-1.025939802553918</v>
       </c>
       <c r="G2">
-        <v>-11.7201302011633</v>
+        <v>-9.695509797347839</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.265220825444381</v>
       </c>
       <c r="E3">
-        <v>-16.03233521654927</v>
+        <v>-16.7467201051553</v>
       </c>
       <c r="F3">
-        <v>-0.9670776716457906</v>
+        <v>-1.10534461668407</v>
       </c>
       <c r="G3">
-        <v>-11.75167307906148</v>
+        <v>-9.31648874910222</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.245703932462408</v>
       </c>
       <c r="E4">
-        <v>-17.37332505359664</v>
+        <v>-16.89512725533467</v>
       </c>
       <c r="F4">
-        <v>-1.106689885346216</v>
+        <v>-1.189733717476867</v>
       </c>
       <c r="G4">
-        <v>-10.49045454496533</v>
+        <v>-8.313535804161239</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.300507868417338</v>
       </c>
       <c r="E5">
-        <v>-19.413909783141</v>
+        <v>-17.8577676175152</v>
       </c>
       <c r="F5">
-        <v>-1.326937038769952</v>
+        <v>-1.128255602310699</v>
       </c>
       <c r="G5">
-        <v>-9.765683431143771</v>
+        <v>-8.002887452938188</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.435712901193399</v>
       </c>
       <c r="E6">
-        <v>-18.12157839930604</v>
+        <v>-17.65289039646017</v>
       </c>
       <c r="F6">
-        <v>-1.287953240426804</v>
+        <v>-0.6530659551643736</v>
       </c>
       <c r="G6">
-        <v>-10.99442220295412</v>
+        <v>-8.422032313119773</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.650538677522166</v>
       </c>
       <c r="E7">
-        <v>-18.82554326922042</v>
+        <v>-18.07315089826801</v>
       </c>
       <c r="F7">
-        <v>-1.412435323515097</v>
+        <v>-0.7423805285342163</v>
       </c>
       <c r="G7">
-        <v>-9.687895542607516</v>
+        <v>-7.753778832744648</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.936947348633562</v>
       </c>
       <c r="E8">
-        <v>-19.6856680368153</v>
+        <v>-18.26694241495226</v>
       </c>
       <c r="F8">
-        <v>-1.49001772935909</v>
+        <v>-0.977082693136803</v>
       </c>
       <c r="G8">
-        <v>-9.837164730427713</v>
+        <v>-7.964064685399154</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.287684755127692</v>
       </c>
       <c r="E9">
-        <v>-19.14328817644262</v>
+        <v>-18.80324053473264</v>
       </c>
       <c r="F9">
-        <v>-1.274797937702945</v>
+        <v>-0.9283672345455669</v>
       </c>
       <c r="G9">
-        <v>-10.28988183292305</v>
+        <v>-7.409753561394665</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.683550647088015</v>
       </c>
       <c r="E10">
-        <v>-20.68330897460111</v>
+        <v>-19.7901037043802</v>
       </c>
       <c r="F10">
-        <v>-1.395776026677396</v>
+        <v>-1.037635521914044</v>
       </c>
       <c r="G10">
-        <v>-8.169282092833036</v>
+        <v>-6.396875600926949</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.100120886120678</v>
       </c>
       <c r="E11">
-        <v>-20.46501388506137</v>
+        <v>-20.0089014545348</v>
       </c>
       <c r="F11">
-        <v>-1.0929257325813</v>
+        <v>-1.053864896069692</v>
       </c>
       <c r="G11">
-        <v>-8.158913464204039</v>
+        <v>-6.465602526322219</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.512723966819</v>
       </c>
       <c r="E12">
-        <v>-21.07371324727638</v>
+        <v>-20.65575773873845</v>
       </c>
       <c r="F12">
-        <v>-0.5460027818221487</v>
+        <v>-1.031190823520264</v>
       </c>
       <c r="G12">
-        <v>-7.38883753467755</v>
+        <v>-6.210703761980494</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.890283604465202</v>
       </c>
       <c r="E13">
-        <v>-21.32253025162783</v>
+        <v>-19.97657267859404</v>
       </c>
       <c r="F13">
-        <v>-0.6614689140983718</v>
+        <v>-0.6800367694321227</v>
       </c>
       <c r="G13">
-        <v>-7.423108302100085</v>
+        <v>-6.007158180043945</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.206172826589651</v>
       </c>
       <c r="E14">
-        <v>-22.61808590895625</v>
+        <v>-21.07892099238521</v>
       </c>
       <c r="F14">
-        <v>-0.8660085648302229</v>
+        <v>-0.6082396815292811</v>
       </c>
       <c r="G14">
-        <v>-6.868224453717303</v>
+        <v>-6.286518565375344</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.442588864349642</v>
       </c>
       <c r="E15">
-        <v>-23.80499894636665</v>
+        <v>-21.13007463477585</v>
       </c>
       <c r="F15">
-        <v>-0.621502672015504</v>
+        <v>-0.4699064670987777</v>
       </c>
       <c r="G15">
-        <v>-7.831960676200077</v>
+        <v>-5.28444291500227</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.584966668638008</v>
       </c>
       <c r="E16">
-        <v>-23.41698117949343</v>
+        <v>-22.74500092149522</v>
       </c>
       <c r="F16">
-        <v>-0.5369503828443557</v>
+        <v>-0.2956345328978177</v>
       </c>
       <c r="G16">
-        <v>-6.871760116353244</v>
+        <v>-4.029742845072951</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>6.627722794004473</v>
       </c>
       <c r="E17">
-        <v>-24.24242689313757</v>
+        <v>-23.99613677728241</v>
       </c>
       <c r="F17">
-        <v>-0.8275035628458934</v>
+        <v>0.0667770341943688</v>
       </c>
       <c r="G17">
-        <v>-6.654551912976122</v>
+        <v>-4.420579230348229</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.57121264154526</v>
       </c>
       <c r="E18">
-        <v>-25.60551115486837</v>
+        <v>-25.07365546808951</v>
       </c>
       <c r="F18">
-        <v>-0.04744406187544663</v>
+        <v>-0.2034206736181768</v>
       </c>
       <c r="G18">
-        <v>-5.472793092913565</v>
+        <v>-4.366167103864767</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.416314638084694</v>
       </c>
       <c r="E19">
-        <v>-25.63289483719275</v>
+        <v>-24.42832075115244</v>
       </c>
       <c r="F19">
-        <v>0.0545337639809921</v>
+        <v>0.1841277023119608</v>
       </c>
       <c r="G19">
-        <v>-6.211091095808589</v>
+        <v>-4.554974137060482</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.171847514862525</v>
       </c>
       <c r="E20">
-        <v>-26.09872537293978</v>
+        <v>-25.06978815128696</v>
       </c>
       <c r="F20">
-        <v>0.04136520737868836</v>
+        <v>0.5174867678531631</v>
       </c>
       <c r="G20">
-        <v>-6.262911065134801</v>
+        <v>-4.145184878572876</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.848573984075433</v>
       </c>
       <c r="E21">
-        <v>-26.4994907941446</v>
+        <v>-25.8924533818904</v>
       </c>
       <c r="F21">
-        <v>0.4419603699029181</v>
+        <v>0.5212069658591356</v>
       </c>
       <c r="G21">
-        <v>-6.304147220371963</v>
+        <v>-4.143635543260498</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.457257236737986</v>
       </c>
       <c r="E22">
-        <v>-26.04803816337193</v>
+        <v>-26.49605821084679</v>
       </c>
       <c r="F22">
-        <v>0.7704287542979921</v>
+        <v>0.7149645864761484</v>
       </c>
       <c r="G22">
-        <v>-5.241869299367242</v>
+        <v>-3.92145490048339</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.01632580461352</v>
       </c>
       <c r="E23">
-        <v>-27.07843808212922</v>
+        <v>-26.46018363975802</v>
       </c>
       <c r="F23">
-        <v>0.2353605694403046</v>
+        <v>1.172674024688598</v>
       </c>
       <c r="G23">
-        <v>-5.235880522486701</v>
+        <v>-3.80390073892941</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.540750997450308</v>
       </c>
       <c r="E24">
-        <v>-28.02022029303042</v>
+        <v>-26.37730350846964</v>
       </c>
       <c r="F24">
-        <v>0.7263712056126975</v>
+        <v>1.262702650759654</v>
       </c>
       <c r="G24">
-        <v>-6.029709616257461</v>
+        <v>-3.961694581513231</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.043742148887539</v>
       </c>
       <c r="E25">
-        <v>-27.97593634570941</v>
+        <v>-27.03096608910682</v>
       </c>
       <c r="F25">
-        <v>0.4975512779373901</v>
+        <v>0.8592214562040711</v>
       </c>
       <c r="G25">
-        <v>-5.783050799762982</v>
+        <v>-4.340387885750463</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.544445894778617</v>
       </c>
       <c r="E26">
-        <v>-28.84754532338775</v>
+        <v>-27.37302890175021</v>
       </c>
       <c r="F26">
-        <v>0.6008859695996144</v>
+        <v>1.238968267934643</v>
       </c>
       <c r="G26">
-        <v>-4.461918012497108</v>
+        <v>-4.759734689209944</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.054616384781282</v>
       </c>
       <c r="E27">
-        <v>-28.63223449821906</v>
+        <v>-27.03132836702743</v>
       </c>
       <c r="F27">
-        <v>0.3916544458983069</v>
+        <v>1.110844681743643</v>
       </c>
       <c r="G27">
-        <v>-6.773784521118513</v>
+        <v>-4.669290585077055</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.583735287795783</v>
       </c>
       <c r="E28">
-        <v>-28.25170682735451</v>
+        <v>-27.02338542361798</v>
       </c>
       <c r="F28">
-        <v>0.9303666189609094</v>
+        <v>0.9008502316643574</v>
       </c>
       <c r="G28">
-        <v>-6.252701342691688</v>
+        <v>-4.827627357129317</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.145685760075313</v>
       </c>
       <c r="E29">
-        <v>-27.99822549477517</v>
+        <v>-27.61758461206043</v>
       </c>
       <c r="F29">
-        <v>0.7282466294126356</v>
+        <v>0.8605915758883015</v>
       </c>
       <c r="G29">
-        <v>-5.378392886861247</v>
+        <v>-5.156933943011701</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.745292638229356</v>
       </c>
       <c r="E30">
-        <v>-28.61661126289259</v>
+        <v>-26.984436018678</v>
       </c>
       <c r="F30">
-        <v>0.6671868397848812</v>
+        <v>0.7213314183340653</v>
       </c>
       <c r="G30">
-        <v>-5.891683041088626</v>
+        <v>-5.586099824540661</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.385195974675579</v>
       </c>
       <c r="E31">
-        <v>-27.13716333306069</v>
+        <v>-26.20232327281326</v>
       </c>
       <c r="F31">
-        <v>0.9124440618339393</v>
+        <v>0.8853133726574499</v>
       </c>
       <c r="G31">
-        <v>-6.204334272362937</v>
+        <v>-5.838283941540182</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.071301731081979</v>
       </c>
       <c r="E32">
-        <v>-27.46637886494432</v>
+        <v>-27.33887515078435</v>
       </c>
       <c r="F32">
-        <v>0.745647315075842</v>
+        <v>1.046361249640118</v>
       </c>
       <c r="G32">
-        <v>-6.114042453324855</v>
+        <v>-5.149087950083628</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.8008055681153567</v>
       </c>
       <c r="E33">
-        <v>-27.4480657160573</v>
+        <v>-25.26464385936301</v>
       </c>
       <c r="F33">
-        <v>-0.09330910823364966</v>
+        <v>0.8928332919400638</v>
       </c>
       <c r="G33">
-        <v>-4.822486079906829</v>
+        <v>-5.408227523261159</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.5703451409021719</v>
       </c>
       <c r="E34">
-        <v>-26.70765568732919</v>
+        <v>-25.5801969851655</v>
       </c>
       <c r="F34">
-        <v>0.2513406050077098</v>
+        <v>0.8676973114695156</v>
       </c>
       <c r="G34">
-        <v>-5.598666655407734</v>
+        <v>-5.135865631199779</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.3785604833965747</v>
       </c>
       <c r="E35">
-        <v>-26.36561551705584</v>
+        <v>-25.33092713341328</v>
       </c>
       <c r="F35">
-        <v>0.8846904403705447</v>
+        <v>1.04191125995228</v>
       </c>
       <c r="G35">
-        <v>-6.55839711778799</v>
+        <v>-4.983395145843105</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.2177120694175205</v>
       </c>
       <c r="E36">
-        <v>-25.42283251339895</v>
+        <v>-25.19236941420059</v>
       </c>
       <c r="F36">
-        <v>0.6580375218209608</v>
+        <v>1.002273879728323</v>
       </c>
       <c r="G36">
-        <v>-6.232258723986689</v>
+        <v>-5.998252812543305</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.08115818853701545</v>
       </c>
       <c r="E37">
-        <v>-25.57776972309738</v>
+        <v>-24.95204329861352</v>
       </c>
       <c r="F37">
-        <v>-0.04555621256446656</v>
+        <v>1.023551324836631</v>
       </c>
       <c r="G37">
-        <v>-6.443550982485133</v>
+        <v>-5.735574266184294</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.03429736907096582</v>
       </c>
       <c r="E38">
-        <v>-24.99671216622518</v>
+        <v>-23.41854350302607</v>
       </c>
       <c r="F38">
-        <v>1.01309401474369</v>
+        <v>0.8974373579648235</v>
       </c>
       <c r="G38">
-        <v>-7.101730472784256</v>
+        <v>-5.569497438661215</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.1333178405900698</v>
       </c>
       <c r="E39">
-        <v>-25.37022975932585</v>
+        <v>-23.8720384755762</v>
       </c>
       <c r="F39">
-        <v>0.6091770989342347</v>
+        <v>1.219501633968854</v>
       </c>
       <c r="G39">
-        <v>-6.793429298348548</v>
+        <v>-4.936335741002365</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2173840233094684</v>
       </c>
       <c r="E40">
-        <v>-24.00149396203348</v>
+        <v>-23.00216843191681</v>
       </c>
       <c r="F40">
-        <v>0.2713208267632339</v>
+        <v>0.7380810072186713</v>
       </c>
       <c r="G40">
-        <v>-6.54009311150136</v>
+        <v>-5.117210707085986</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.2851214762043787</v>
       </c>
       <c r="E41">
-        <v>-23.50892731574517</v>
+        <v>-22.95337412448417</v>
       </c>
       <c r="F41">
-        <v>0.7578508236538843</v>
+        <v>0.9571941256679741</v>
       </c>
       <c r="G41">
-        <v>-6.298535845682898</v>
+        <v>-4.826634193467536</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3358673820359839</v>
       </c>
       <c r="E42">
-        <v>-25.37411971849844</v>
+        <v>-22.55820589715283</v>
       </c>
       <c r="F42">
-        <v>0.1683299075731714</v>
+        <v>1.087592408747061</v>
       </c>
       <c r="G42">
-        <v>-5.911711841601218</v>
+        <v>-4.886174354991328</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3678171615057372</v>
       </c>
       <c r="E43">
-        <v>-22.79927921095116</v>
+        <v>-22.11762160399856</v>
       </c>
       <c r="F43">
-        <v>0.2466213959139611</v>
+        <v>0.7165550518895234</v>
       </c>
       <c r="G43">
-        <v>-7.440544945455426</v>
+        <v>-5.292384913750982</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3790292592925029</v>
       </c>
       <c r="E44">
-        <v>-24.56030765458</v>
+        <v>-22.31486834635066</v>
       </c>
       <c r="F44">
-        <v>0.1270026578475041</v>
+        <v>0.751051584011706</v>
       </c>
       <c r="G44">
-        <v>-5.525149370617139</v>
+        <v>-5.026534864765348</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.369281412982601</v>
       </c>
       <c r="E45">
-        <v>-22.44264829742509</v>
+        <v>-21.59759429132774</v>
       </c>
       <c r="F45">
-        <v>0.7609687985580217</v>
+        <v>1.017769320365091</v>
       </c>
       <c r="G45">
-        <v>-6.106408335311295</v>
+        <v>-5.390724668995032</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.339745178142821</v>
       </c>
       <c r="E46">
-        <v>-21.15180678153866</v>
+        <v>-20.67761668277348</v>
       </c>
       <c r="F46">
-        <v>0.07051379954839736</v>
+        <v>0.6516872573110997</v>
       </c>
       <c r="G46">
-        <v>-7.242974898217261</v>
+        <v>-4.828041175321726</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.2930556399241154</v>
       </c>
       <c r="E47">
-        <v>-20.7927576628925</v>
+        <v>-21.05859267256477</v>
       </c>
       <c r="F47">
-        <v>0.2912198685132836</v>
+        <v>0.4620938396279601</v>
       </c>
       <c r="G47">
-        <v>-6.48103960017184</v>
+        <v>-5.068039174191191</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2326913423081729</v>
       </c>
       <c r="E48">
-        <v>-21.23888933670616</v>
+        <v>-20.48802306149434</v>
       </c>
       <c r="F48">
-        <v>0.5301790131988571</v>
+        <v>0.8182272101743291</v>
       </c>
       <c r="G48">
-        <v>-7.572963456480735</v>
+        <v>-5.061335319474167</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.1627346966915921</v>
       </c>
       <c r="E49">
-        <v>-21.84980312271093</v>
+        <v>-20.87463247295118</v>
       </c>
       <c r="F49">
-        <v>0.1705789250717721</v>
+        <v>0.9105172792550277</v>
       </c>
       <c r="G49">
-        <v>-6.369805270052328</v>
+        <v>-4.78155780540482</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.08746450108171423</v>
       </c>
       <c r="E50">
-        <v>-19.30688835691772</v>
+        <v>-20.03263971528301</v>
       </c>
       <c r="F50">
-        <v>0.3704059936490968</v>
+        <v>0.5725135576863286</v>
       </c>
       <c r="G50">
-        <v>-8.129270839445404</v>
+        <v>-5.158158844861231</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.01072453759502752</v>
       </c>
       <c r="E51">
-        <v>-19.66954214087399</v>
+        <v>-19.56349886503638</v>
       </c>
       <c r="F51">
-        <v>0.03587975843735004</v>
+        <v>0.2697601825763596</v>
       </c>
       <c r="G51">
-        <v>-7.595680419971213</v>
+        <v>-5.416874668209736</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.06386295551497821</v>
       </c>
       <c r="E52">
-        <v>-19.11601317749442</v>
+        <v>-19.13240172492818</v>
       </c>
       <c r="F52">
-        <v>0.4109520929139242</v>
+        <v>0.1449765737534477</v>
       </c>
       <c r="G52">
-        <v>-7.11892875686077</v>
+        <v>-5.414024288500423</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.1334352738770809</v>
       </c>
       <c r="E53">
-        <v>-19.22465126893843</v>
+        <v>-18.04034663255645</v>
       </c>
       <c r="F53">
-        <v>0.1598308580204485</v>
+        <v>0.4956899363832996</v>
       </c>
       <c r="G53">
-        <v>-7.273200178990807</v>
+        <v>-5.525953833183181</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.196759036431717</v>
       </c>
       <c r="E54">
-        <v>-17.65592900251932</v>
+        <v>-19.05813927967639</v>
       </c>
       <c r="F54">
-        <v>0.21832436543433</v>
+        <v>0.2949276410082142</v>
       </c>
       <c r="G54">
-        <v>-7.479036658440532</v>
+        <v>-5.600014047442217</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.2528634992375894</v>
       </c>
       <c r="E55">
-        <v>-18.59375332713782</v>
+        <v>-18.49693455285382</v>
       </c>
       <c r="F55">
-        <v>0.2249993499660884</v>
+        <v>0.4831948424794719</v>
       </c>
       <c r="G55">
-        <v>-7.239717321406618</v>
+        <v>-5.214855247766789</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.301563940473673</v>
       </c>
       <c r="E56">
-        <v>-18.16364339436329</v>
+        <v>-18.24362077381276</v>
       </c>
       <c r="F56">
-        <v>0.5253695120582031</v>
+        <v>0.2532019465618003</v>
       </c>
       <c r="G56">
-        <v>-8.201040156191263</v>
+        <v>-5.973777949371473</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.3440009755677473</v>
       </c>
       <c r="E57">
-        <v>-18.47528391862315</v>
+        <v>-17.64489311136263</v>
       </c>
       <c r="F57">
-        <v>0.4394056848326844</v>
+        <v>0.4671932693595938</v>
       </c>
       <c r="G57">
-        <v>-7.785778565927243</v>
+        <v>-6.508593270695195</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.3809879290857622</v>
       </c>
       <c r="E58">
-        <v>-17.64309530718158</v>
+        <v>-18.21116520059978</v>
       </c>
       <c r="F58">
-        <v>0.3249161977243619</v>
+        <v>0.1648847275449283</v>
       </c>
       <c r="G58">
-        <v>-7.650320974096885</v>
+        <v>-5.293745547967622</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.4141124768032537</v>
       </c>
       <c r="E59">
-        <v>-17.5118057887512</v>
+        <v>-17.67809135431286</v>
       </c>
       <c r="F59">
-        <v>0.1689660937385214</v>
+        <v>0.1561520783846159</v>
       </c>
       <c r="G59">
-        <v>-8.192790276707401</v>
+        <v>-5.867833871023717</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.4455777642873193</v>
       </c>
       <c r="E60">
-        <v>-16.58772085427198</v>
+        <v>-17.54915664236647</v>
       </c>
       <c r="F60">
-        <v>-0.3087127974532163</v>
+        <v>0.3892952555351339</v>
       </c>
       <c r="G60">
-        <v>-7.886667441236533</v>
+        <v>-6.058104165347789</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.4766692773916786</v>
       </c>
       <c r="E61">
-        <v>-18.62753121476103</v>
+        <v>-17.27512509474031</v>
       </c>
       <c r="F61">
-        <v>0.02549782977806383</v>
+        <v>0.5117511519561793</v>
       </c>
       <c r="G61">
-        <v>-7.50816614864058</v>
+        <v>-6.264271699351442</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.5089117797645882</v>
       </c>
       <c r="E62">
-        <v>-17.93313501042486</v>
+        <v>-16.82136747069773</v>
       </c>
       <c r="F62">
-        <v>0.3352641633201334</v>
+        <v>0.2836825535152109</v>
       </c>
       <c r="G62">
-        <v>-8.72257025826589</v>
+        <v>-6.214600274080217</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5438565355097226</v>
       </c>
       <c r="E63">
-        <v>-16.54984469767183</v>
+        <v>-16.51757932036718</v>
       </c>
       <c r="F63">
-        <v>0.2062368282926796</v>
+        <v>0.2874806180570467</v>
       </c>
       <c r="G63">
-        <v>-7.830911233264128</v>
+        <v>-5.765859136777546</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.5817121282151004</v>
       </c>
       <c r="E64">
-        <v>-17.39123063982297</v>
+        <v>-16.32188584459971</v>
       </c>
       <c r="F64">
-        <v>0.1869383529096595</v>
+        <v>-0.01537050440645258</v>
       </c>
       <c r="G64">
-        <v>-7.061633145212603</v>
+        <v>-6.506196435724762</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6227577864636952</v>
       </c>
       <c r="E65">
-        <v>-17.42937850486359</v>
+        <v>-17.14264458764591</v>
       </c>
       <c r="F65">
-        <v>-0.2424914505386182</v>
+        <v>0.3766709363164694</v>
       </c>
       <c r="G65">
-        <v>-8.644752574819782</v>
+        <v>-6.131114936670876</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.6672762232038295</v>
       </c>
       <c r="E66">
-        <v>-16.96548162751784</v>
+        <v>-17.42013588941393</v>
       </c>
       <c r="F66">
-        <v>-0.3520107332301436</v>
+        <v>0.3134598765436448</v>
       </c>
       <c r="G66">
-        <v>-8.423796833892204</v>
+        <v>-6.170560086771292</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.71446659320866</v>
       </c>
       <c r="E67">
-        <v>-17.27603984648986</v>
+        <v>-16.32598864205066</v>
       </c>
       <c r="F67">
-        <v>-0.3724357882809711</v>
+        <v>0.06412128830099358</v>
       </c>
       <c r="G67">
-        <v>-7.826415512421797</v>
+        <v>-5.325424158232908</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.7646552966554854</v>
       </c>
       <c r="E68">
-        <v>-15.77306196571411</v>
+        <v>-16.86748544999185</v>
       </c>
       <c r="F68">
-        <v>-0.423172463335038</v>
+        <v>-0.2111369159752541</v>
       </c>
       <c r="G68">
-        <v>-9.275911392427373</v>
+        <v>-5.443647049985821</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.8188597869684084</v>
       </c>
       <c r="E69">
-        <v>-16.51473091021635</v>
+        <v>-16.89548500478127</v>
       </c>
       <c r="F69">
-        <v>-0.1827545636531347</v>
+        <v>-0.2859534030612999</v>
       </c>
       <c r="G69">
-        <v>-8.350233201464059</v>
+        <v>-5.956030114735441</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.8770705600366077</v>
       </c>
       <c r="E70">
-        <v>-16.08928983414374</v>
+        <v>-17.30539794348159</v>
       </c>
       <c r="F70">
-        <v>-0.7041008424834483</v>
+        <v>-0.0589053532605806</v>
       </c>
       <c r="G70">
-        <v>-8.30862295458096</v>
+        <v>-6.376558782952442</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.9406395617088354</v>
       </c>
       <c r="E71">
-        <v>-17.78291647064241</v>
+        <v>-15.8809211596288</v>
       </c>
       <c r="F71">
-        <v>-0.09226702204092789</v>
+        <v>-0.3678673420545318</v>
       </c>
       <c r="G71">
-        <v>-7.947038549690682</v>
+        <v>-6.296367438354676</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.011131589434503</v>
       </c>
       <c r="E72">
-        <v>-17.41209331957631</v>
+        <v>-15.99095854954118</v>
       </c>
       <c r="F72">
-        <v>-0.608219800711614</v>
+        <v>-0.2149681152132019</v>
       </c>
       <c r="G72">
-        <v>-7.765789491961124</v>
+        <v>-5.842965052932712</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.088270804970911</v>
       </c>
       <c r="E73">
-        <v>-14.81328812758044</v>
+        <v>-15.73587866563713</v>
       </c>
       <c r="F73">
-        <v>-0.6717796031610173</v>
+        <v>-0.373175520371671</v>
       </c>
       <c r="G73">
-        <v>-8.58761917990304</v>
+        <v>-6.367683210361656</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.173499009112446</v>
       </c>
       <c r="E74">
-        <v>-15.72445332571577</v>
+        <v>-17.42240918336578</v>
       </c>
       <c r="F74">
-        <v>-0.01288705893285966</v>
+        <v>-0.6760200158959478</v>
       </c>
       <c r="G74">
-        <v>-7.765653759594014</v>
+        <v>-6.311946865662486</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.268106512175424</v>
       </c>
       <c r="E75">
-        <v>-16.26542483067207</v>
+        <v>-17.95049717977026</v>
       </c>
       <c r="F75">
-        <v>-0.3871997805010667</v>
+        <v>-0.5244014450593459</v>
       </c>
       <c r="G75">
-        <v>-7.276954337632341</v>
+        <v>-6.167352168143738</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.371228909898319</v>
       </c>
       <c r="E76">
-        <v>-18.47528391862315</v>
+        <v>-17.77006013293464</v>
       </c>
       <c r="F76">
-        <v>-0.4008653575450501</v>
+        <v>-0.6529764914848712</v>
       </c>
       <c r="G76">
-        <v>-8.377591549800597</v>
+        <v>-5.933442262520994</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.48384837494947</v>
       </c>
       <c r="E77">
-        <v>-18.26310679746776</v>
+        <v>-17.57960610159405</v>
       </c>
       <c r="F77">
-        <v>-0.7534988758145913</v>
+        <v>-0.7492949112453837</v>
       </c>
       <c r="G77">
-        <v>-7.349720128585521</v>
+        <v>-5.234288150082311</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.606279126334429</v>
       </c>
       <c r="E78">
-        <v>-17.85941598205399</v>
+        <v>-18.21464306863767</v>
       </c>
       <c r="F78">
-        <v>-0.5289640927139656</v>
+        <v>-0.8647154833144529</v>
       </c>
       <c r="G78">
-        <v>-7.619873886772207</v>
+        <v>-5.55916853657869</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.736103376352447</v>
       </c>
       <c r="E79">
-        <v>-17.84467127068501</v>
+        <v>-19.02966876359017</v>
       </c>
       <c r="F79">
-        <v>-0.8455089567131435</v>
+        <v>-0.8814402211769748</v>
       </c>
       <c r="G79">
-        <v>-6.524298498733497</v>
+        <v>-5.664476990182906</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.873164438833279</v>
       </c>
       <c r="E80">
-        <v>-19.74495481852373</v>
+        <v>-19.85050901916851</v>
       </c>
       <c r="F80">
-        <v>-0.915748713898722</v>
+        <v>-0.7525719326908586</v>
       </c>
       <c r="G80">
-        <v>-7.671505155002681</v>
+        <v>-6.237419864482413</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.016260518097193</v>
       </c>
       <c r="E81">
-        <v>-19.84171472264562</v>
+        <v>-20.36805925655714</v>
       </c>
       <c r="F81">
-        <v>-0.8627762752244992</v>
+        <v>-0.8951157386297919</v>
       </c>
       <c r="G81">
-        <v>-7.227259738542341</v>
+        <v>-5.587311484208033</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.161269591457085</v>
       </c>
       <c r="E82">
-        <v>-19.93319895454858</v>
+        <v>-19.88075469706574</v>
       </c>
       <c r="F82">
-        <v>-0.6884852885732748</v>
+        <v>-0.5925735972075369</v>
       </c>
       <c r="G82">
-        <v>-6.52237838232072</v>
+        <v>-4.98005811593952</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.306751290360388</v>
       </c>
       <c r="E83">
-        <v>-20.24481230796439</v>
+        <v>-21.73169599211688</v>
       </c>
       <c r="F83">
-        <v>-1.176010154714688</v>
+        <v>-0.8620373715012021</v>
       </c>
       <c r="G83">
-        <v>-7.70993727816808</v>
+        <v>-5.871104690016517</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.449481985262429</v>
       </c>
       <c r="E84">
-        <v>-22.83871316260995</v>
+        <v>-22.47367287285164</v>
       </c>
       <c r="F84">
-        <v>-1.664368358463316</v>
+        <v>-1.07649175167716</v>
       </c>
       <c r="G84">
-        <v>-7.562786839493015</v>
+        <v>-5.742728355094659</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.58386308768475</v>
       </c>
       <c r="E85">
-        <v>-22.73369785037208</v>
+        <v>-23.14151863408085</v>
       </c>
       <c r="F85">
-        <v>-1.55872500684949</v>
+        <v>-0.938158537246657</v>
       </c>
       <c r="G85">
-        <v>-7.346621457960763</v>
+        <v>-5.210511812019265</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.707346279363115</v>
       </c>
       <c r="E86">
-        <v>-24.6427258815196</v>
+        <v>-25.29074145506921</v>
       </c>
       <c r="F86">
-        <v>-1.51856575516177</v>
+        <v>-1.122291357010542</v>
       </c>
       <c r="G86">
-        <v>-6.494811469615208</v>
+        <v>-5.063775191536609</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.815902560652204</v>
       </c>
       <c r="E87">
-        <v>-25.45423748064215</v>
+        <v>-25.14473892458791</v>
       </c>
       <c r="F87">
-        <v>-1.534988967289673</v>
+        <v>-1.560848112502865</v>
       </c>
       <c r="G87">
-        <v>-7.35068018679191</v>
+        <v>-5.626859261220167</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.904643948159134</v>
       </c>
       <c r="E88">
-        <v>-25.80890303644888</v>
+        <v>-26.31856467211615</v>
       </c>
       <c r="F88">
-        <v>-1.336524563089953</v>
+        <v>-1.187350504459013</v>
       </c>
       <c r="G88">
-        <v>-8.305438209772181</v>
+        <v>-5.009386238871923</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.972431107113737</v>
       </c>
       <c r="E89">
-        <v>-27.93090972865115</v>
+        <v>-26.87106114342197</v>
       </c>
       <c r="F89">
-        <v>-1.618878562538582</v>
+        <v>-1.607452890951768</v>
       </c>
       <c r="G89">
-        <v>-7.305352197268209</v>
+        <v>-5.854982333240266</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.017478251052102</v>
       </c>
       <c r="E90">
-        <v>-28.17852215891655</v>
+        <v>-29.42847381875073</v>
       </c>
       <c r="F90">
-        <v>-1.46677788187355</v>
+        <v>-2.041289608982939</v>
       </c>
       <c r="G90">
-        <v>-6.960783996449785</v>
+        <v>-4.20003730761306</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.038383860524301</v>
       </c>
       <c r="E91">
-        <v>-28.42701764161346</v>
+        <v>-29.96561649893355</v>
       </c>
       <c r="F91">
-        <v>-1.154019485272569</v>
+        <v>-1.989268964454533</v>
       </c>
       <c r="G91">
-        <v>-6.638939380212919</v>
+        <v>-5.604781233018768</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.03859882077893</v>
       </c>
       <c r="E92">
-        <v>-31.2869912508167</v>
+        <v>-31.48563955587417</v>
       </c>
       <c r="F92">
-        <v>-1.509967301520711</v>
+        <v>-2.034859821202409</v>
       </c>
       <c r="G92">
-        <v>-7.446258947056209</v>
+        <v>-6.221969548450635</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.021070257338484</v>
       </c>
       <c r="E93">
-        <v>-33.11789178414689</v>
+        <v>-34.13195749715852</v>
       </c>
       <c r="F93">
-        <v>-1.560694864533347</v>
+        <v>-1.946760462812474</v>
       </c>
       <c r="G93">
-        <v>-7.23871091556268</v>
+        <v>-6.37974683830676</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.990074860532636</v>
       </c>
       <c r="E94">
-        <v>-34.33324363832546</v>
+        <v>-35.15614208534029</v>
       </c>
       <c r="F94">
-        <v>-1.825615043622657</v>
+        <v>-2.006531312761472</v>
       </c>
       <c r="G94">
-        <v>-8.259226304589495</v>
+        <v>-5.608780372030207</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.954185991476347</v>
       </c>
       <c r="E95">
-        <v>-35.86506337005606</v>
+        <v>-37.66688883602001</v>
       </c>
       <c r="F95">
-        <v>-2.267065286452958</v>
+        <v>-2.308413245363696</v>
       </c>
       <c r="G95">
-        <v>-7.638684406526346</v>
+        <v>-6.399136703530271</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.921194941296082</v>
       </c>
       <c r="E96">
-        <v>-40.5459612843506</v>
+        <v>-39.17937198373787</v>
       </c>
       <c r="F96">
-        <v>-2.260308293548323</v>
+        <v>-2.877078355344125</v>
       </c>
       <c r="G96">
-        <v>-7.624472234526255</v>
+        <v>-6.204602426551618</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.89706001097512</v>
       </c>
       <c r="E97">
-        <v>-40.48047049325167</v>
+        <v>-41.75441174414148</v>
       </c>
       <c r="F97">
-        <v>-2.216354290788378</v>
+        <v>-2.844882199499517</v>
       </c>
       <c r="G97">
-        <v>-7.900061908488424</v>
+        <v>-6.355361359864489</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.893820560995403</v>
       </c>
       <c r="E98">
-        <v>-43.97658375291941</v>
+        <v>-42.37454776746287</v>
       </c>
       <c r="F98">
-        <v>-3.219170898413043</v>
+        <v>-3.174571597446318</v>
       </c>
       <c r="G98">
-        <v>-8.34605198244796</v>
+        <v>-6.51660810144577</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.912242940745762</v>
       </c>
       <c r="E99">
-        <v>-44.45553780634066</v>
+        <v>-45.27332134196383</v>
       </c>
       <c r="F99">
-        <v>-3.143830883128428</v>
+        <v>-3.098964019490598</v>
       </c>
       <c r="G99">
-        <v>-8.330929410424568</v>
+        <v>-6.756248561396993</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.961775752387981</v>
       </c>
       <c r="E100">
-        <v>-47.08445735048755</v>
+        <v>-46.60400663640675</v>
       </c>
       <c r="F100">
-        <v>-3.187208342176024</v>
+        <v>-3.650265720340947</v>
       </c>
       <c r="G100">
-        <v>-9.506063828863045</v>
+        <v>-7.318071313230089</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.034872958306553</v>
       </c>
       <c r="E101">
-        <v>-49.20671537299724</v>
+        <v>-48.92226493879794</v>
       </c>
       <c r="F101">
-        <v>-3.247853948102378</v>
+        <v>-3.851378415127417</v>
       </c>
       <c r="G101">
-        <v>-8.713118650751271</v>
+        <v>-7.579041618090836</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.144233118573941</v>
       </c>
       <c r="E102">
-        <v>-50.39239440124055</v>
+        <v>-50.29622999145067</v>
       </c>
       <c r="F102">
-        <v>-3.529948668553931</v>
+        <v>-4.014124445285825</v>
       </c>
       <c r="G102">
-        <v>-9.529787198197463</v>
+        <v>-8.088806041318893</v>
       </c>
     </row>
   </sheetData>
